--- a/files/202604/成绩单/汇总.xlsx
+++ b/files/202604/成绩单/汇总.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\cyril\code\files\202604\成绩单\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C5D56F-5702-48E1-8789-998E82A1D7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFCA9FC-A9B2-44B8-9186-A26DE01ECEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="19416" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4104" yWindow="2244" windowWidth="23040" windowHeight="14100" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2068,14 +2068,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -42796,41 +42796,41 @@
       <c r="B1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="13" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="13" t="s">
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="13" t="s">
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="14"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="13"/>
       <c r="AB1" s="11" t="s">
         <v>603</v>
       </c>
@@ -42853,47 +42853,47 @@
     <row r="2" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="13" t="s">
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13" t="s">
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="13" t="s">
+      <c r="N2" s="12"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13" t="s">
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="T2" s="13"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="13" t="s">
+      <c r="T2" s="12"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13" t="s">
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="14"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="13"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="11"/>
       <c r="AD2" s="11"/>
@@ -42904,7 +42904,7 @@
     <row r="3" spans="1:67" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
+      <c r="C3" s="14"/>
       <c r="D3" s="2" t="s">
         <v>611</v>
       </c>
@@ -43145,6 +43145,7 @@
         <v>1936</v>
       </c>
       <c r="AG4" s="6">
+        <f>RANK(AF4, $AF$4:$AF$166)</f>
         <v>1</v>
       </c>
       <c r="AJ4" s="4"/>
@@ -43309,6 +43310,7 @@
         <v>1927</v>
       </c>
       <c r="AG5" s="6">
+        <f t="shared" ref="AG5:AG68" si="0">RANK(AF5, $AF$4:$AF$166)</f>
         <v>2</v>
       </c>
     </row>
@@ -43441,6 +43443,7 @@
         <v>1876</v>
       </c>
       <c r="AG6" s="6">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -43573,6 +43576,7 @@
         <v>1851</v>
       </c>
       <c r="AG7" s="6">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -43705,6 +43709,7 @@
         <v>1796</v>
       </c>
       <c r="AG8" s="6">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -43837,6 +43842,7 @@
         <v>1777</v>
       </c>
       <c r="AG9" s="6">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -43969,6 +43975,7 @@
         <v>1750</v>
       </c>
       <c r="AG10" s="6">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -44101,6 +44108,7 @@
         <v>1749</v>
       </c>
       <c r="AG11" s="6">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -44233,6 +44241,7 @@
         <v>1742</v>
       </c>
       <c r="AG12" s="6">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
@@ -44365,6 +44374,7 @@
         <v>1734</v>
       </c>
       <c r="AG13" s="6">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -44497,6 +44507,7 @@
         <v>1718</v>
       </c>
       <c r="AG14" s="6">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -44629,6 +44640,7 @@
         <v>1681</v>
       </c>
       <c r="AG15" s="6">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -44761,6 +44773,7 @@
         <v>1657</v>
       </c>
       <c r="AG16" s="6">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
@@ -44893,6 +44906,7 @@
         <v>1640</v>
       </c>
       <c r="AG17" s="6">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -45025,6 +45039,7 @@
         <v>1589</v>
       </c>
       <c r="AG18" s="6">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
@@ -45157,6 +45172,7 @@
         <v>1580</v>
       </c>
       <c r="AG19" s="6">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
@@ -45289,6 +45305,7 @@
         <v>1568</v>
       </c>
       <c r="AG20" s="6">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
@@ -45421,6 +45438,7 @@
         <v>1558</v>
       </c>
       <c r="AG21" s="6">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
@@ -45553,6 +45571,7 @@
         <v>1542</v>
       </c>
       <c r="AG22" s="6">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
@@ -45685,6 +45704,7 @@
         <v>1532</v>
       </c>
       <c r="AG23" s="6">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
@@ -45817,6 +45837,7 @@
         <v>1525</v>
       </c>
       <c r="AG24" s="6">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
@@ -45949,6 +45970,7 @@
         <v>1523</v>
       </c>
       <c r="AG25" s="6">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
@@ -46081,6 +46103,7 @@
         <v>1517</v>
       </c>
       <c r="AG26" s="6">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
@@ -46213,6 +46236,7 @@
         <v>1492</v>
       </c>
       <c r="AG27" s="6">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
@@ -46345,6 +46369,7 @@
         <v>1487</v>
       </c>
       <c r="AG28" s="6">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
@@ -46477,6 +46502,7 @@
         <v>1476</v>
       </c>
       <c r="AG29" s="6">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
@@ -46609,6 +46635,7 @@
         <v>1472</v>
       </c>
       <c r="AG30" s="6">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
@@ -46741,6 +46768,7 @@
         <v>1471</v>
       </c>
       <c r="AG31" s="6">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
@@ -46873,6 +46901,7 @@
         <v>1454</v>
       </c>
       <c r="AG32" s="6">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
     </row>
@@ -47005,6 +47034,7 @@
         <v>1435</v>
       </c>
       <c r="AG33" s="6">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
@@ -47137,6 +47167,7 @@
         <v>1434</v>
       </c>
       <c r="AG34" s="6">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
@@ -47269,6 +47300,7 @@
         <v>1411</v>
       </c>
       <c r="AG35" s="6">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -47401,6 +47433,7 @@
         <v>1403</v>
       </c>
       <c r="AG36" s="6">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
@@ -47533,6 +47566,7 @@
         <v>1395</v>
       </c>
       <c r="AG37" s="6">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
@@ -47665,6 +47699,7 @@
         <v>1365</v>
       </c>
       <c r="AG38" s="6">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
@@ -47797,6 +47832,7 @@
         <v>1354</v>
       </c>
       <c r="AG39" s="6">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
@@ -47929,7 +47965,8 @@
         <v>1354</v>
       </c>
       <c r="AG40" s="6">
-        <v>37</v>
+        <f t="shared" si="0"/>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -48061,6 +48098,7 @@
         <v>1338</v>
       </c>
       <c r="AG41" s="6">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
@@ -48193,6 +48231,7 @@
         <v>1303</v>
       </c>
       <c r="AG42" s="6">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
     </row>
@@ -48325,6 +48364,7 @@
         <v>1296</v>
       </c>
       <c r="AG43" s="6">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
@@ -48457,6 +48497,7 @@
         <v>1295</v>
       </c>
       <c r="AG44" s="6">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
     </row>
@@ -48589,6 +48630,7 @@
         <v>1293</v>
       </c>
       <c r="AG45" s="6">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
@@ -48721,6 +48763,7 @@
         <v>1289</v>
       </c>
       <c r="AG46" s="6">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
     </row>
@@ -48853,6 +48896,7 @@
         <v>1285</v>
       </c>
       <c r="AG47" s="6">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
     </row>
@@ -48985,6 +49029,7 @@
         <v>1278</v>
       </c>
       <c r="AG48" s="6">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
@@ -49117,6 +49162,7 @@
         <v>1267</v>
       </c>
       <c r="AG49" s="6">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
     </row>
@@ -49249,6 +49295,7 @@
         <v>1266</v>
       </c>
       <c r="AG50" s="6">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
     </row>
@@ -49381,6 +49428,7 @@
         <v>1241</v>
       </c>
       <c r="AG51" s="6">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
     </row>
@@ -49513,6 +49561,7 @@
         <v>1228</v>
       </c>
       <c r="AG52" s="6">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
     </row>
@@ -49645,6 +49694,7 @@
         <v>1224</v>
       </c>
       <c r="AG53" s="6">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
@@ -49777,6 +49827,7 @@
         <v>1221</v>
       </c>
       <c r="AG54" s="6">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
     </row>
@@ -49909,6 +49960,7 @@
         <v>1220</v>
       </c>
       <c r="AG55" s="6">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
@@ -50041,6 +50093,7 @@
         <v>1215</v>
       </c>
       <c r="AG56" s="6">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
     </row>
@@ -50173,6 +50226,7 @@
         <v>1197</v>
       </c>
       <c r="AG57" s="6">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
     </row>
@@ -50305,6 +50359,7 @@
         <v>1193</v>
       </c>
       <c r="AG58" s="6">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
     </row>
@@ -50437,6 +50492,7 @@
         <v>1192</v>
       </c>
       <c r="AG59" s="6">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
@@ -50569,7 +50625,8 @@
         <v>1192</v>
       </c>
       <c r="AG60" s="6">
-        <v>57</v>
+        <f t="shared" si="0"/>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -50701,6 +50758,7 @@
         <v>1185</v>
       </c>
       <c r="AG61" s="6">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
@@ -50833,6 +50891,7 @@
         <v>1180</v>
       </c>
       <c r="AG62" s="6">
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
@@ -50965,6 +51024,7 @@
         <v>1174</v>
       </c>
       <c r="AG63" s="6">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
@@ -51097,6 +51157,7 @@
         <v>1172</v>
       </c>
       <c r="AG64" s="6">
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
@@ -51229,6 +51290,7 @@
         <v>1168</v>
       </c>
       <c r="AG65" s="6">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
     </row>
@@ -51361,6 +51423,7 @@
         <v>1162</v>
       </c>
       <c r="AG66" s="6">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
     </row>
@@ -51493,6 +51556,7 @@
         <v>1160</v>
       </c>
       <c r="AG67" s="6">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
     </row>
@@ -51625,6 +51689,7 @@
         <v>1152</v>
       </c>
       <c r="AG68" s="6">
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
     </row>
@@ -51757,6 +51822,7 @@
         <v>1139</v>
       </c>
       <c r="AG69" s="6">
+        <f t="shared" ref="AG69:AG132" si="1">RANK(AF69, $AF$4:$AF$166)</f>
         <v>66</v>
       </c>
     </row>
@@ -51889,6 +51955,7 @@
         <v>1122</v>
       </c>
       <c r="AG70" s="6">
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
     </row>
@@ -52021,6 +52088,7 @@
         <v>1109</v>
       </c>
       <c r="AG71" s="6">
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
     </row>
@@ -52153,6 +52221,7 @@
         <v>1105</v>
       </c>
       <c r="AG72" s="6">
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
     </row>
@@ -52285,6 +52354,7 @@
         <v>1103</v>
       </c>
       <c r="AG73" s="6">
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
     </row>
@@ -52417,6 +52487,7 @@
         <v>1102</v>
       </c>
       <c r="AG74" s="6">
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
     </row>
@@ -52549,6 +52620,7 @@
         <v>1101</v>
       </c>
       <c r="AG75" s="6">
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
     </row>
@@ -52681,6 +52753,7 @@
         <v>1100</v>
       </c>
       <c r="AG76" s="6">
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
     </row>
@@ -52813,6 +52886,7 @@
         <v>1096</v>
       </c>
       <c r="AG77" s="6">
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
     </row>
@@ -52945,6 +53019,7 @@
         <v>1094</v>
       </c>
       <c r="AG78" s="6">
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
     </row>
@@ -53077,7 +53152,8 @@
         <v>1094</v>
       </c>
       <c r="AG79" s="6">
-        <v>76</v>
+        <f t="shared" si="1"/>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -53209,6 +53285,7 @@
         <v>1083</v>
       </c>
       <c r="AG80" s="6">
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
     </row>
@@ -53341,6 +53418,7 @@
         <v>1082</v>
       </c>
       <c r="AG81" s="6">
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
     </row>
@@ -53473,6 +53551,7 @@
         <v>1081</v>
       </c>
       <c r="AG82" s="6">
+        <f t="shared" si="1"/>
         <v>79</v>
       </c>
     </row>
@@ -53605,6 +53684,7 @@
         <v>1076</v>
       </c>
       <c r="AG83" s="6">
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
@@ -53737,6 +53817,7 @@
         <v>1068</v>
       </c>
       <c r="AG84" s="6">
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
     </row>
@@ -53869,6 +53950,7 @@
         <v>1058</v>
       </c>
       <c r="AG85" s="6">
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
     </row>
@@ -54001,7 +54083,8 @@
         <v>1058</v>
       </c>
       <c r="AG86" s="6">
-        <v>83</v>
+        <f t="shared" si="1"/>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -54133,6 +54216,7 @@
         <v>1056</v>
       </c>
       <c r="AG87" s="6">
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
     </row>
@@ -54265,6 +54349,7 @@
         <v>1052</v>
       </c>
       <c r="AG88" s="6">
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
     </row>
@@ -54397,6 +54482,7 @@
         <v>1041</v>
       </c>
       <c r="AG89" s="6">
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
     </row>
@@ -54529,6 +54615,7 @@
         <v>1039</v>
       </c>
       <c r="AG90" s="6">
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
     </row>
@@ -54661,6 +54748,7 @@
         <v>1027</v>
       </c>
       <c r="AG91" s="6">
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
     </row>
@@ -54793,6 +54881,7 @@
         <v>1022</v>
       </c>
       <c r="AG92" s="6">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
     </row>
@@ -54925,6 +55014,7 @@
         <v>1017</v>
       </c>
       <c r="AG93" s="6">
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
     </row>
@@ -55057,6 +55147,7 @@
         <v>1007</v>
       </c>
       <c r="AG94" s="6">
+        <f t="shared" si="1"/>
         <v>91</v>
       </c>
     </row>
@@ -55189,6 +55280,7 @@
         <v>995</v>
       </c>
       <c r="AG95" s="6">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
     </row>
@@ -55321,6 +55413,7 @@
         <v>986</v>
       </c>
       <c r="AG96" s="6">
+        <f t="shared" si="1"/>
         <v>93</v>
       </c>
     </row>
@@ -55453,6 +55546,7 @@
         <v>977</v>
       </c>
       <c r="AG97" s="6">
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
     </row>
@@ -55585,6 +55679,7 @@
         <v>976</v>
       </c>
       <c r="AG98" s="6">
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
     </row>
@@ -55717,6 +55812,7 @@
         <v>969</v>
       </c>
       <c r="AG99" s="6">
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
     </row>
@@ -55849,6 +55945,7 @@
         <v>968</v>
       </c>
       <c r="AG100" s="6">
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
     </row>
@@ -55981,6 +56078,7 @@
         <v>961</v>
       </c>
       <c r="AG101" s="6">
+        <f t="shared" si="1"/>
         <v>98</v>
       </c>
     </row>
@@ -56113,6 +56211,7 @@
         <v>951</v>
       </c>
       <c r="AG102" s="6">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
     </row>
@@ -56245,6 +56344,7 @@
         <v>947</v>
       </c>
       <c r="AG103" s="6">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
@@ -56377,6 +56477,7 @@
         <v>944</v>
       </c>
       <c r="AG104" s="6">
+        <f t="shared" si="1"/>
         <v>101</v>
       </c>
     </row>
@@ -56509,6 +56610,7 @@
         <v>936</v>
       </c>
       <c r="AG105" s="6">
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
     </row>
@@ -56641,6 +56743,7 @@
         <v>928</v>
       </c>
       <c r="AG106" s="6">
+        <f t="shared" si="1"/>
         <v>103</v>
       </c>
     </row>
@@ -56773,6 +56876,7 @@
         <v>927</v>
       </c>
       <c r="AG107" s="6">
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
     </row>
@@ -56905,6 +57009,7 @@
         <v>926</v>
       </c>
       <c r="AG108" s="6">
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
     </row>
@@ -57037,6 +57142,7 @@
         <v>918</v>
       </c>
       <c r="AG109" s="6">
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
     </row>
@@ -57169,6 +57275,7 @@
         <v>904</v>
       </c>
       <c r="AG110" s="6">
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
     </row>
@@ -57301,6 +57408,7 @@
         <v>902</v>
       </c>
       <c r="AG111" s="6">
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
     </row>
@@ -57433,6 +57541,7 @@
         <v>899</v>
       </c>
       <c r="AG112" s="6">
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
     </row>
@@ -57565,6 +57674,7 @@
         <v>895</v>
       </c>
       <c r="AG113" s="6">
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
     </row>
@@ -57697,6 +57807,7 @@
         <v>894</v>
       </c>
       <c r="AG114" s="6">
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
     </row>
@@ -57829,6 +57940,7 @@
         <v>890</v>
       </c>
       <c r="AG115" s="6">
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
     </row>
@@ -57961,6 +58073,7 @@
         <v>885</v>
       </c>
       <c r="AG116" s="6">
+        <f t="shared" si="1"/>
         <v>113</v>
       </c>
     </row>
@@ -58093,6 +58206,7 @@
         <v>881</v>
       </c>
       <c r="AG117" s="6">
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
     </row>
@@ -58225,6 +58339,7 @@
         <v>875</v>
       </c>
       <c r="AG118" s="6">
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
     </row>
@@ -58357,7 +58472,8 @@
         <v>875</v>
       </c>
       <c r="AG119" s="6">
-        <v>116</v>
+        <f t="shared" si="1"/>
+        <v>115</v>
       </c>
     </row>
     <row r="120" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -58489,6 +58605,7 @@
         <v>872</v>
       </c>
       <c r="AG120" s="6">
+        <f t="shared" si="1"/>
         <v>117</v>
       </c>
     </row>
@@ -58621,6 +58738,7 @@
         <v>860</v>
       </c>
       <c r="AG121" s="6">
+        <f t="shared" si="1"/>
         <v>118</v>
       </c>
     </row>
@@ -58753,6 +58871,7 @@
         <v>848</v>
       </c>
       <c r="AG122" s="6">
+        <f t="shared" si="1"/>
         <v>119</v>
       </c>
     </row>
@@ -58885,7 +59004,8 @@
         <v>848</v>
       </c>
       <c r="AG123" s="6">
-        <v>120</v>
+        <f t="shared" si="1"/>
+        <v>119</v>
       </c>
     </row>
     <row r="124" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -59017,6 +59137,7 @@
         <v>847</v>
       </c>
       <c r="AG124" s="6">
+        <f t="shared" si="1"/>
         <v>121</v>
       </c>
     </row>
@@ -59149,6 +59270,7 @@
         <v>803</v>
       </c>
       <c r="AG125" s="6">
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
     </row>
@@ -59281,6 +59403,7 @@
         <v>800</v>
       </c>
       <c r="AG126" s="6">
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
     </row>
@@ -59413,6 +59536,7 @@
         <v>798</v>
       </c>
       <c r="AG127" s="6">
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
     </row>
@@ -59545,6 +59669,7 @@
         <v>793</v>
       </c>
       <c r="AG128" s="6">
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
     </row>
@@ -59677,6 +59802,7 @@
         <v>790</v>
       </c>
       <c r="AG129" s="6">
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
     </row>
@@ -59809,6 +59935,7 @@
         <v>786</v>
       </c>
       <c r="AG130" s="6">
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
     </row>
@@ -59941,6 +60068,7 @@
         <v>766</v>
       </c>
       <c r="AG131" s="6">
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
     </row>
@@ -60073,6 +60201,7 @@
         <v>748</v>
       </c>
       <c r="AG132" s="6">
+        <f t="shared" si="1"/>
         <v>129</v>
       </c>
     </row>
@@ -60205,6 +60334,7 @@
         <v>722</v>
       </c>
       <c r="AG133" s="6">
+        <f t="shared" ref="AG133:AG166" si="2">RANK(AF133, $AF$4:$AF$166)</f>
         <v>130</v>
       </c>
     </row>
@@ -60337,6 +60467,7 @@
         <v>707</v>
       </c>
       <c r="AG134" s="6">
+        <f t="shared" si="2"/>
         <v>131</v>
       </c>
     </row>
@@ -60469,6 +60600,7 @@
         <v>689</v>
       </c>
       <c r="AG135" s="6">
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
     </row>
@@ -60601,6 +60733,7 @@
         <v>686</v>
       </c>
       <c r="AG136" s="6">
+        <f t="shared" si="2"/>
         <v>133</v>
       </c>
     </row>
@@ -60733,6 +60866,7 @@
         <v>683</v>
       </c>
       <c r="AG137" s="6">
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
     </row>
@@ -60865,6 +60999,7 @@
         <v>673</v>
       </c>
       <c r="AG138" s="6">
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
     </row>
@@ -60997,6 +61132,7 @@
         <v>672</v>
       </c>
       <c r="AG139" s="6">
+        <f t="shared" si="2"/>
         <v>136</v>
       </c>
     </row>
@@ -61129,6 +61265,7 @@
         <v>658</v>
       </c>
       <c r="AG140" s="6">
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
     </row>
@@ -61261,6 +61398,7 @@
         <v>626</v>
       </c>
       <c r="AG141" s="6">
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
     </row>
@@ -61393,6 +61531,7 @@
         <v>618</v>
       </c>
       <c r="AG142" s="6">
+        <f t="shared" si="2"/>
         <v>139</v>
       </c>
     </row>
@@ -61525,6 +61664,7 @@
         <v>616</v>
       </c>
       <c r="AG143" s="6">
+        <f t="shared" si="2"/>
         <v>140</v>
       </c>
     </row>
@@ -61657,6 +61797,7 @@
         <v>604</v>
       </c>
       <c r="AG144" s="6">
+        <f t="shared" si="2"/>
         <v>141</v>
       </c>
     </row>
@@ -61789,6 +61930,7 @@
         <v>593</v>
       </c>
       <c r="AG145" s="6">
+        <f t="shared" si="2"/>
         <v>142</v>
       </c>
     </row>
@@ -61921,6 +62063,7 @@
         <v>577</v>
       </c>
       <c r="AG146" s="6">
+        <f t="shared" si="2"/>
         <v>143</v>
       </c>
     </row>
@@ -62053,6 +62196,7 @@
         <v>560</v>
       </c>
       <c r="AG147" s="6">
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
     </row>
@@ -62185,6 +62329,7 @@
         <v>555</v>
       </c>
       <c r="AG148" s="6">
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
     </row>
@@ -62317,6 +62462,7 @@
         <v>551</v>
       </c>
       <c r="AG149" s="6">
+        <f t="shared" si="2"/>
         <v>146</v>
       </c>
     </row>
@@ -62449,6 +62595,7 @@
         <v>545</v>
       </c>
       <c r="AG150" s="6">
+        <f t="shared" si="2"/>
         <v>147</v>
       </c>
     </row>
@@ -62581,6 +62728,7 @@
         <v>540</v>
       </c>
       <c r="AG151" s="6">
+        <f t="shared" si="2"/>
         <v>148</v>
       </c>
     </row>
@@ -62713,6 +62861,7 @@
         <v>519</v>
       </c>
       <c r="AG152" s="6">
+        <f t="shared" si="2"/>
         <v>149</v>
       </c>
     </row>
@@ -62845,6 +62994,7 @@
         <v>501</v>
       </c>
       <c r="AG153" s="6">
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
     </row>
@@ -62977,6 +63127,7 @@
         <v>467</v>
       </c>
       <c r="AG154" s="6">
+        <f t="shared" si="2"/>
         <v>151</v>
       </c>
     </row>
@@ -63109,6 +63260,7 @@
         <v>441</v>
       </c>
       <c r="AG155" s="6">
+        <f t="shared" si="2"/>
         <v>152</v>
       </c>
     </row>
@@ -63241,6 +63393,7 @@
         <v>438</v>
       </c>
       <c r="AG156" s="6">
+        <f t="shared" si="2"/>
         <v>153</v>
       </c>
     </row>
@@ -63373,6 +63526,7 @@
         <v>434</v>
       </c>
       <c r="AG157" s="6">
+        <f t="shared" si="2"/>
         <v>154</v>
       </c>
     </row>
@@ -63505,6 +63659,7 @@
         <v>397</v>
       </c>
       <c r="AG158" s="6">
+        <f t="shared" si="2"/>
         <v>155</v>
       </c>
     </row>
@@ -63637,6 +63792,7 @@
         <v>385</v>
       </c>
       <c r="AG159" s="6">
+        <f t="shared" si="2"/>
         <v>156</v>
       </c>
     </row>
@@ -63769,6 +63925,7 @@
         <v>360</v>
       </c>
       <c r="AG160" s="6">
+        <f t="shared" si="2"/>
         <v>157</v>
       </c>
     </row>
@@ -63901,6 +64058,7 @@
         <v>347</v>
       </c>
       <c r="AG161" s="6">
+        <f t="shared" si="2"/>
         <v>158</v>
       </c>
     </row>
@@ -64033,6 +64191,7 @@
         <v>346</v>
       </c>
       <c r="AG162" s="6">
+        <f t="shared" si="2"/>
         <v>159</v>
       </c>
     </row>
@@ -64165,6 +64324,7 @@
         <v>342</v>
       </c>
       <c r="AG163" s="6">
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
     </row>
@@ -64297,6 +64457,7 @@
         <v>316</v>
       </c>
       <c r="AG164" s="6">
+        <f t="shared" si="2"/>
         <v>161</v>
       </c>
     </row>
@@ -64429,6 +64590,7 @@
         <v>255</v>
       </c>
       <c r="AG165" s="6">
+        <f t="shared" si="2"/>
         <v>162</v>
       </c>
     </row>
@@ -64561,6 +64723,7 @@
         <v>242</v>
       </c>
       <c r="AG166" s="6">
+        <f t="shared" si="2"/>
         <v>163</v>
       </c>
     </row>
@@ -66549,6 +66712,11 @@
     <sortCondition ref="AF4:AF166"/>
   </sortState>
   <mergeCells count="21">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:O1"/>
     <mergeCell ref="AE1:AE3"/>
     <mergeCell ref="AF1:AF3"/>
     <mergeCell ref="AG1:AG3"/>
@@ -66565,11 +66733,6 @@
     <mergeCell ref="AB1:AB3"/>
     <mergeCell ref="AC1:AC3"/>
     <mergeCell ref="AD1:AD3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="J1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D2 H1:I2 J1:J2 M1:M2 K1:L2 N1:O2 E1:F2 G1:G2 P1:P2">
     <cfRule type="colorScale" priority="12">
@@ -66701,6 +66864,20 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AC4:AF166">
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{00A00003-00D4-4D72-908B-003800950003}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AD1:AD1048576 BM3:BM4">
     <cfRule type="dataBar" priority="2">
       <dataBar>
@@ -66725,20 +66902,6 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{00F600BA-008C-4F2B-98FF-002300F000E1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AF166">
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00A00003-00D4-4D72-908B-003800950003}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -66900,6 +67063,17 @@
           <xm:sqref>AC167:AC1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{00A00003-00D4-4D72-908B-003800950003}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor indexed="2"/>
+              <x14:axisColor indexed="64"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AC4:AF166</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{00730068-003B-4D66-9AD6-000500BE0034}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -66920,17 +67094,6 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>AD3</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00A00003-00D4-4D72-908B-003800950003}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor indexed="2"/>
-              <x14:axisColor indexed="64"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>AC4:AF166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{003D009C-00DD-4CC3-9063-008000BD00D5}">
